--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9120" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="用例" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -40,7 +40,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
@@ -48,7 +48,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
@@ -56,14 +56,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -71,7 +71,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
@@ -79,7 +79,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -87,7 +87,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -95,7 +95,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -103,14 +103,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
@@ -118,7 +118,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
@@ -126,7 +126,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
@@ -134,14 +134,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
@@ -149,35 +149,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color theme="0"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -638,68 +638,74 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1074,85 +1080,85 @@
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" style="4" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="52" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>用例编号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>接口名称</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>用例描述</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>是否执行</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>请求方式</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>请求路径</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>请求头</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>查询参数</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>请求体</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>变量提取</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>断言</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>超时(秒)</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="100.8" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>album_list_001</t>
@@ -1190,17 +1196,21 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1209,7 +1219,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="100.8" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>album_list_002</t>
@@ -1247,17 +1257,21 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>{"ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>{"ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1266,7 +1280,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="100.8" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>album_list_003</t>
@@ -1304,17 +1318,21 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1323,7 +1341,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="100.8" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>album_list_004</t>
@@ -1361,17 +1379,21 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1380,7 +1402,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="100.8" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>album_list_005</t>
@@ -1418,15 +1440,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
@@ -1437,7 +1463,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="100.8" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>album_list_006</t>
@@ -1475,15 +1501,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 9, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
@@ -1494,7 +1524,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="100.8" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>album_list_007</t>
@@ -1532,17 +1562,21 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1551,7 +1585,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="100.8" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>album_list_008</t>
@@ -1589,17 +1623,21 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1608,7 +1646,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="100.8" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>album_list_009</t>
@@ -1646,17 +1684,21 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1665,7 +1707,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="100.8" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>album_list_010</t>
@@ -1703,17 +1745,21 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1722,7 +1768,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="100.8" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>album_list_011</t>
@@ -1760,17 +1806,21 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1779,7 +1829,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="100.8" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>album_list_012</t>
@@ -1817,17 +1867,21 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1836,7 +1890,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="100.8" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>album_list_013</t>
@@ -1874,17 +1928,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1893,7 +1951,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="100.8" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>album_list_014</t>
@@ -1931,17 +1989,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1950,7 +2012,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="100.8" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>album_list_015</t>
@@ -1988,17 +2050,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 99, "sectionType": 0, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 99, "sectionType": 1, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2007,7 +2073,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="100.8" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>album_list_016</t>
@@ -2045,17 +2111,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>/album/atlas/list</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>{"Authorization":"{{token}}"}</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 0, "pageInfo": {"pageSize": -1, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+          <t>/atlas/list</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Authorization": "{{token}}",
+  "x-yun-api-version": "v2",
+  "Content-Type": "application/json"
+}</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumType": 1, "sectionType": 1, "pageInfo": {"pageSize": -1, "pageCursor": "0"}, "orderBy": 2, "orderDirection": 1, "needTotalCount": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2140,7 +2210,6 @@
           <t>token</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>真实值请填本地 data/secret_vars.xlsx（不入库），此处留空</t>
@@ -2153,7 +2222,7 @@
           <t>user_id</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
+      <c r="B5" s="7" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>真实值请填本地 data/secret_vars.xlsx（不入库），此处留空</t>
@@ -2552,7 +2621,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="28.8" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>示例</t>

--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -1201,11 +1201,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>{
-  "Authorization": "{{token}}",
-  "x-yun-api-version": "v2",
-  "Content-Type": "application/json"
-}</t>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v2", "Content-Type": "application/json"}</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">

--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2125,6 +2125,462 @@
         </is>
       </c>
       <c r="M17" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>album_file_list_001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>冒烟：全参数正常请求，预期返回正常（列表数据、入库正常）</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>album_file_list_002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>userId不传：预期报错（鉴权失败 01000002）</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>{"ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "false"], ["eq", "$.code", "01000002"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>album_file_list_003</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ownerType不传：预期返回正常（默认值兜底）</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>album_file_list_004</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>albumId为空(null)：预期报错（albumId不能为空 01000001）</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": null, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "false"], ["eq", "$.code", "01000001"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>album_file_list_005</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>pageInfo为空(null)：实际报错（pageInfo不能为空 01000001；原表预期'返回正常'与实际不符，pageInfo实为必填）</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": null, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "false"], ["eq", "$.code", "01000001"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>album_file_list_008</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>imageThumbnailStyleList为空([])：预期返回正常（默认缩略图样式）</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": [], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>album_file_list_009</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>expireSec为空(null)：预期返回正常（默认过期时间兜底）</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": null}</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>album_file_list_017</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>albumId类型变更为string：预期返回正常（服务端兼容字符串ID）</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": "1312418529655752781", "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>

--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2585,6 +2585,426 @@
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>album_file_list_006</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>orderBy不传：预期返回正常（排序字段走默认）</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderDirection": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>album_file_list_007</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>orderDirection不传：预期返回正常（排序方向走默认）</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>album_file_list_010</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>不指定排序：预期返回正常（默认按拍摄时间/本地创建时间/上传时间排序）</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>album_file_list_011</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>我的相簿图片(自定义相册ID)：预期返回正常</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1313031550338106146, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>album_file_list_012</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>人物相册图片：预期返回正常</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>album_file_list_013</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>事物相册图片：预期返回正常</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655751361, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>album_file_list_014</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>地点相册图片：预期返回正常</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312064319407449806, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2632,19 +2632,16 @@
           <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderDirection": 1, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2692,19 +2689,16 @@
           <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "orderBy": 2, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2752,19 +2746,16 @@
           <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2812,19 +2803,16 @@
           <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1313031550338106146, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2872,19 +2860,16 @@
           <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2932,19 +2917,16 @@
           <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312418529655751361, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2992,19 +2974,73 @@
           <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1312064319407449806, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>album_file_list_016</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>三方鉴权：x-yun-neauth 系列头 + 三方 userId(2920388198605357056)，不带 Authorization；当前三方头为占位值，实际返回鉴权失败 01000002（与原表标记 fail 一致；如需正向用例请提供真实 app-key/neauth）</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{"x-yun-app-key": "x-yun-app-key", "x-yun-rand": "x-yun-rand", "x-yun-tid": "x-yun-tid", "x-yun-neauth": "x-yun-neauth", "x-yun-neauth-version": "x-yun-neauth-version", "Content-Type": "application/json", "x-yun-api-version": "v1"}</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>{"userId": "2920388198605357056", "ownerType": "personal", "albumId": 1312418529655752781, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "false"], ["eq", "$.code", "01000002"]]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3039,6 +3039,63 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "false"], ["eq", "$.code", "01000002"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>album_file_list_015</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>相册-图片列表</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>统一相册图片列表(分页)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>回忆相册图片（albumId 1313032203173143149）：预期返回正常</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>/atlas/file/list</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "ownerType": "personal", "albumId": 1313032203173143149, "pageInfo": {"pageSize": 10, "pageCursor": "0"}, "imageThumbnailStyleList": ["Big"], "expireSec": 86400}</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
     </row>

--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3096,6 +3096,804 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["eq", "$.success", "true"], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ai_music_list_001</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>模板音乐列表接口</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>冒烟-正常入参</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/recommend/music/list</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null, "pageSize": 10}</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ai_music_list_002</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>模板音乐列表接口</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>userId不传</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/recommend/music/list</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>{"channelId": "10030113270", "pageCursor": null, "pageSize": 10}</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ai_music_list_003</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>模板音乐列表接口</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>channelId不传</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/recommend/music/list</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "pageCursor": null, "pageSize": 10}</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ai_music_list_004</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>模板音乐列表接口</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>pageCursor不传</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/recommend/music/list</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageSize": 10}</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ai_music_list_005</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>模板音乐列表接口</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>pageSize不传</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/recommend/music/list</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null}</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ai_music_list_006</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>模板音乐列表接口</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>text不传</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/recommend/music/list</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null, "pageSize": 10}</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ai_music_list_007</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>模板音乐列表接口</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>text指定模板</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/recommend/music/list</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null, "pageSize": 10, "text": "轻快"}</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ai_config_get_001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>查询模型与token计算公式接口</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>冒烟-正常入参</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/audiocreation/config/get</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>{"channelId": "10030113270", "userId": "{{user_id}}"}</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ai_config_get_002</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>查询模型与token计算公式接口</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>channelId不传</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/audiocreation/config/get</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}"}</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ai_config_get_003</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>查询模型与token计算公式接口</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>userId不传（实际可选）</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/audiocreation/config/get</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>{"channelId": "10030113270"}</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ai_task_del_001</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>音频任务删除接口</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>正常入参（需失败任务ID，暂不执行）</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>{"channelId": "10030113270", "userId": "{{user_id}}", "taskIds": ["{{fail_task_id}}"]}</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["eq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ai_task_del_002</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>音频任务删除接口</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>taskIds不传</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>{"channelId": "10030113270", "userId": "{{user_id}}"}</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ai_task_del_003</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>音频任务删除接口</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>taskIds传不存在的ID</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>{"channelId": "10030113270", "userId": "{{user_id}}", "taskIds": ["nonexist_99999"]}</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ai_task_del_004</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>一键成片·AI音频</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>音频任务删除接口</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>channelId不传</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>{"userId": "{{user_id}}", "taskIds": ["fake_id"]}</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
         </is>
       </c>
     </row>

--- a/data/api_cases.xlsx
+++ b/data/api_cases.xlsx
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3102,7 +3102,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ai_music_list_001</t>
+          <t>ai_task_del_001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>模板音乐列表接口</t>
+          <t>音频任务删除接口</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>冒烟-正常入参</t>
+          <t>正常入参（需失败任务ID，暂不执行）</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>/ai/api/audio/recommend/music/list</t>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3147,19 +3147,19 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null, "pageSize": 10}</t>
+          <t>{"channelId": "10030113270", "userId": "{{user_id}}", "taskIds": ["{{fail_task_id}}"]}</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+          <t>[["eq", "status_code", 200], ["eq", "$.code", "0000"]]</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ai_music_list_002</t>
+          <t>ai_task_del_002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>模板音乐列表接口</t>
+          <t>音频任务删除接口</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>userId不传</t>
+          <t>taskIds不传</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>/ai/api/audio/recommend/music/list</t>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3204,19 +3204,19 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>{"channelId": "10030113270", "pageCursor": null, "pageSize": 10}</t>
+          <t>{"channelId": "10030113270", "userId": "{{user_id}}"}</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
+          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ai_music_list_003</t>
+          <t>ai_task_del_003</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>模板音乐列表接口</t>
+          <t>音频任务删除接口</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>channelId不传</t>
+          <t>taskIds传不存在的ID</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>/ai/api/audio/recommend/music/list</t>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>{"userId": "{{user_id}}", "pageCursor": null, "pageSize": 10}</t>
+          <t>{"channelId": "10030113270", "userId": "{{user_id}}", "taskIds": ["nonexist_99999"]}</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
+          <t>[["eq", "status_code", 200]]</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ai_music_list_004</t>
+          <t>ai_task_del_004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>模板音乐列表接口</t>
+          <t>音频任务删除接口</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pageCursor不传</t>
+          <t>channelId不传</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>/ai/api/audio/recommend/music/list</t>
+          <t>/ai/api/audio/audiocreation/task/delete</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3318,580 +3318,10 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageSize": 10}</t>
+          <t>{"userId": "{{user_id}}", "taskIds": ["fake_id"]}</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ai_music_list_005</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>模板音乐列表接口</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>pageSize不传</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/recommend/music/list</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null}</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ai_music_list_006</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>模板音乐列表接口</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>text不传</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/recommend/music/list</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null, "pageSize": 10}</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ai_music_list_007</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>模板音乐列表接口</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>text指定模板</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/recommend/music/list</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "channelId": "10030113270", "pageCursor": null, "pageSize": 10, "text": "轻快"}</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ai_config_get_001</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>查询模型与token计算公式接口</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>冒烟-正常入参</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/audiocreation/config/get</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>{"channelId": "10030113270", "userId": "{{user_id}}"}</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ai_config_get_002</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>查询模型与token计算公式接口</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>channelId不传</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/audiocreation/config/get</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}"}</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ai_config_get_003</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>查询模型与token计算公式接口</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>userId不传（实际可选）</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/audiocreation/config/get</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>{"channelId": "10030113270"}</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["not_null", "$.data"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ai_task_del_001</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>音频任务删除接口</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>正常入参（需失败任务ID，暂不执行）</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/audiocreation/task/delete</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>{"channelId": "10030113270", "userId": "{{user_id}}", "taskIds": ["{{fail_task_id}}"]}</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["eq", "$.code", "0000"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ai_task_del_002</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>音频任务删除接口</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>taskIds不传</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/audiocreation/task/delete</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>{"channelId": "10030113270", "userId": "{{user_id}}"}</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ai_task_del_003</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>音频任务删除接口</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>taskIds传不存在的ID</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/audiocreation/task/delete</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>{"channelId": "10030113270", "userId": "{{user_id}}", "taskIds": ["nonexist_99999"]}</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>[["eq", "status_code", 200]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ai_task_del_004</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>一键成片·AI音频</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>音频任务删除接口</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>channelId不传</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>/ai/api/audio/audiocreation/task/delete</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>{"Authorization": "{{token}}", "x-yun-api-version": "v1", "Content-Type": "application/json"}</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>{"userId": "{{user_id}}", "taskIds": ["fake_id"]}</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
         <is>
           <t>[["eq", "status_code", 200], ["neq", "$.code", "0000"]]</t>
         </is>
